--- a/daily_matches/job_matches_2026-06-26.xlsx
+++ b/daily_matches/job_matches_2026-06-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. SW Engineer</t>
+          <t>Advisory Associate, AI - Summer 2026 (Houston)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>BDO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>26.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, MongoDB, NoSQL, Python</t>
+          <t>RAG, TensorFlow, PyTorch, AWS SageMaker, S3, Glue, Athena, Redshift, Synapse, Data Lake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd564ef34bae6dc8</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5fd57bbd10ca27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>(USA) Data Scientist III</t>
+          <t>Senior Data Scientist – Manufacturing Intelligence, Machine Learning &amp; AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Wa-Ni Village, TN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>23.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, BigQuery, Dataflow, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a71642e67c198fce</t>
+          <t>https://www.indeed.com/viewjob?jk=2ab95f94071e971b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Senior Backend Software Engineer IV</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Vida Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>RAG, Copilot, BigQuery, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=797e64bcb8624035</t>
+          <t>https://www.indeed.com/viewjob?jk=3a816a575de11cfe</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>RAG, Data Lake, CI/CD, Jenkins, Terraform, Git, Snowflake, Databricks, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eefab3368870cfd6</t>
+          <t>https://www.indeed.com/viewjob?jk=171509f615b5daa2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Full-Stack Java Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Clayton, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>RAG, Copilot, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=992d1d915f9d6362</t>
+          <t>https://www.indeed.com/viewjob?jk=651520622efc1265</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pleasant Hill, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>LangChain, RAG, LLaMA, Pinecone, BigQuery, FastAPI, Git, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=654b2f67eee1d48c</t>
+          <t>https://www.indeed.com/viewjob?jk=a691be2740e13cbd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Research Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=438aec656ad718b9</t>
+          <t>https://www.indeed.com/viewjob?jk=a169ce2550ba6168</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>AI Agentic Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>RAG, Gemini, FAISS, Pinecone, Docker, Kubernetes, CI/CD, Git, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9d760938954181</t>
+          <t>https://www.indeed.com/viewjob?jk=388a8cbd02740969</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Martinez, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6d712eb3900bf51</t>
+          <t>https://www.indeed.com/viewjob?jk=5abd4df6140552c4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Associate Quality Engineer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AdvancedMD</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R</t>
+          <t>RAG, Prompt Engineering, Data Lake, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,42 +811,1407 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5594afadd444db81</t>
+          <t>https://www.indeed.com/viewjob?jk=89c86aac6f960c5b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marketing Data Scientist Senior Associate - Consumer Bank</t>
+          <t>Senior Integration Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>ServiceTitan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, CI/CD, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ce4996222dad233</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sr AI Engineer I - Global Servicing Technology</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Sunrise, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, TensorFlow, PyTorch, BigQuery, Docker, Kubernetes, BigQuery, Python</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fbf7ed6afa3038c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Engineer II - Global Servicing Technology</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Sunrise, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, BigQuery, Kafka, Tableau, Power BI, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c63a2ab17c26b27</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Java Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Labcorp</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Kubernetes, CI/CD, Jenkins, Git, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec4bd51618d0a580</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Software Engineer - Banking Platforms</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Instantiations</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75c1a9dd3a6ab3dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Guidewire Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Office Ally</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Walnut Creek, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e37631ce8845786</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Guidewire Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Office Ally</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Concord, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0e4bf24557f7446</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Guidewire Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Office Ally</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Clayton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=943f1767bc3da17e</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Guidewire Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Office Ally</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Antioch, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55a3ba405f74d032</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Guidewire Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Office Ally</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Martinez, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53e9315332f2ea0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Guidewire Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Office Ally</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Pleasant Hill, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ae88819d628f2aed</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Guidewire Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Office Ally</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48ff3521016f8dd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AI Security Engineer (GRC)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SCAN Health Plan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Lakewood, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Copilot, Hugging Face, Cortex, Git, Snowflake, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4e97e8edd3a2abd</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst - Corporate Financial</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>oura</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0d0e3250352dd44</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Associate, Modelling Data Scientist</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BlackRock</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, MLflow, PostgreSQL, MySQL, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43627dd021296a58</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Real Estate Data Scientist - Remote</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Harbor Freight Tools</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Calabasas, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a333269a7a1a658e</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AI &amp; Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Stored Energy Systems</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Longmont, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Git, Power BI, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14fb94404a5ee275</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Data Scientist Geospatial Analytics</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Bunge</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Chesterfield, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, BigQuery, BigQuery, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0df42bfc02a5f701</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NewYork-Presbyterian Hospital</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Manhattan, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a889968da2ddc13e</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Associate</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BlackRock</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Git, Kafka, Cassandra, NoSQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eaad1b10fdb8d092</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>DevOps and Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Booz Allen Hamilton</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58a6a360953a1f79</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Software Engineer - Automation, Early Career</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Viasat</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Carlsbad, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e05d0af611ab8d76</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Yield Solutions Group LLC</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Centennial, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, CI/CD, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68121ab049612e6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Full Stack Python Developer Active Secret Clearance Requ Herndon VA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Innovative Tech Solutions</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, Databricks, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6dc3bdf5d64e1ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - AI (.Net)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Momentive Software</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce369a125b1def8c</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Software Engineer II - AI (.Net)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Momentive Software</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=146470e0e0fd5922</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AI Quality Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Momentive Software</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Gemini, Pinecone, Prompt Engineering, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81175184ac69abaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Software Developer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Neomax</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Chantilly, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Keras, spaCy, MLflow, FastAPI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3b161f030038d4e</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sr Scientist, Tech</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>PySpark, Hadoop, Tableau, Matplotlib, Python, SQL, R, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d43651fd738ad37a</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Asylon</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Norristown, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6713335c51820324</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Frontend Engineer/UX Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Asylon</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Norristown, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Git, MongoDB, NoSQL, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e01952c4a3f71b76</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Acrisure LLC</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Gemini, Kubernetes, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc29356aa7c08c47</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Application Software Engineer - Testing</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0af81836b7e21cc9</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Software Development Engineer II – Geoprocessing and Map Viewer Analysis</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Esri</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Redlands, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=712ad52a7ca693ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Enterprise AI Enablement Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Zywave, Inc.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, CI/CD, Git, Snowflake, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd93b504042602c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Software Engineer III -Python Fullstack - AI/ML</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>JPMorganChase</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, Git, Tableau, Python, SQL, R, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e9cee8192469523f</t>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=024da5907788aedb</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer (Onsite Hybrid)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Databricks, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5812a02c32719af</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Sr Mgr. Software Engineering</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Sunrise, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d930713a7cd6b8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Assistant Research Scientist PREP0004601</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Johns Hopkins University</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Gaithersburg, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, PostgreSQL, MongoDB, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6bfda1b82787c0e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, Long Island City, New York</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Bloomingdale's</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Long Island City, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eac7651c61492267</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-26.xlsx
+++ b/daily_matches/job_matches_2026-06-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Advisory Associate, AI - Summer 2026 (Houston)</t>
+          <t>Senior Associate - AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BDO</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.7</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, AWS SageMaker, S3, Glue, Athena, Redshift, Synapse, Data Lake</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Keras, spaCy</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5fd57bbd10ca27</t>
+          <t>https://www.indeed.com/viewjob?jk=c986febe6201a3ba</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Scientist – Manufacturing Intelligence, Machine Learning &amp; AI</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>U.S. Financial Technology</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wa-Ni Village, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.3</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, BigQuery, Dataflow, FastAPI, Docker, Kubernetes</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ab95f94071e971b</t>
+          <t>https://www.indeed.com/viewjob?jk=a593e5a13bf91848</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer IV</t>
+          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vida Health</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Manayunk, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, BigQuery, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, AWS SageMaker, AKS, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,409 +566,409 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a816a575de11cfe</t>
+          <t>https://www.indeed.com/viewjob?jk=b74ecbc2e66a148f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Data</t>
+          <t>Senior Robotics Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Jenkins, Terraform, Git, Snowflake, Databricks, MongoDB, Cassandra</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, CI/CD, Kafka, Hadoop, PostgreSQL, Cassandra, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=171509f615b5daa2</t>
+          <t>https://www.indeed.com/viewjob?jk=f7d4e995adafbb96</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Full-Stack Java Developer</t>
+          <t>Senior Software Engineer, AI-Augmented Backend</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>WEX Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=651520622efc1265</t>
+          <t>https://www.indeed.com/viewjob?jk=73c154bd36b952fa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Asylon</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Norristown, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Pinecone, BigQuery, FastAPI, Git, BigQuery, Python, SQL</t>
+          <t>S3, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a691be2740e13cbd</t>
+          <t>https://www.indeed.com/viewjob?jk=c73c430d87b81058</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Research Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Git</t>
+          <t>S3, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a169ce2550ba6168</t>
+          <t>https://www.indeed.com/viewjob?jk=25cb408b4789fdc2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Agentic Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Gemini, FAISS, Pinecone, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=388a8cbd02740969</t>
+          <t>https://www.indeed.com/viewjob?jk=1b9a38e235659081</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5abd4df6140552c4</t>
+          <t>https://www.indeed.com/viewjob?jk=cd0775a42f899524</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Data Lake, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c86aac6f960c5b</t>
+          <t>https://www.indeed.com/viewjob?jk=b33138f7850dfefc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Integration Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, CI/CD, Git, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ce4996222dad233</t>
+          <t>https://www.indeed.com/viewjob?jk=a342726a84e27f8e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr AI Engineer I - Global Servicing Technology</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, TensorFlow, PyTorch, BigQuery, Docker, Kubernetes, BigQuery, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbf7ed6afa3038c6</t>
+          <t>https://www.indeed.com/viewjob?jk=c186d8b7ac65fdf8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer II - Global Servicing Technology</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, BigQuery, Kafka, Tableau, Power BI, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c63a2ab17c26b27</t>
+          <t>https://www.indeed.com/viewjob?jk=95cc142f3e2617a6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Java Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Labcorp</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Kubernetes, CI/CD, Jenkins, Git, Kafka, Python, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec4bd51618d0a580</t>
+          <t>https://www.indeed.com/viewjob?jk=db16f20add9ea986</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer - Banking Platforms</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Instantiations</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c1a9dd3a6ab3dd</t>
+          <t>https://www.indeed.com/viewjob?jk=1382d06b80fb6867</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Guidewire Integration Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e37631ce8845786</t>
+          <t>https://www.indeed.com/viewjob?jk=bcad5c4e643319ff</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Guidewire Integration Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Concord, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0e4bf24557f7446</t>
+          <t>https://www.indeed.com/viewjob?jk=40e64526422d931b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Guidewire Integration Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Clayton, CA, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=943f1767bc3da17e</t>
+          <t>https://www.indeed.com/viewjob?jk=e4d627fd3422104c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Guidewire Integration Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Antioch, CA, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a3ba405f74d032</t>
+          <t>https://www.indeed.com/viewjob?jk=fab8211cf6bde1e0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Guidewire Integration Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Martinez, CA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53e9315332f2ea0c</t>
+          <t>https://www.indeed.com/viewjob?jk=05bab721c73d545f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Guidewire Integration Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pleasant Hill, CA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae88819d628f2aed</t>
+          <t>https://www.indeed.com/viewjob?jk=85a706af297ba804</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Guidewire Integration Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Office Ally</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48ff3521016f8dd5</t>
+          <t>https://www.indeed.com/viewjob?jk=13401bc8d0f3279e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Security Engineer (GRC)</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lakewood, CA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Hugging Face, Cortex, Git, Snowflake, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4e97e8edd3a2abd</t>
+          <t>https://www.indeed.com/viewjob?jk=31032458d140d1ae</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Analyst - Corporate Financial</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>oura</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0d0e3250352dd44</t>
+          <t>https://www.indeed.com/viewjob?jk=115cfe00112809d8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Associate, Modelling Data Scientist</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, MLflow, PostgreSQL, MySQL, Tableau, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43627dd021296a58</t>
+          <t>https://www.indeed.com/viewjob?jk=031a5b8865d1f458</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Real Estate Data Scientist - Remote</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Harbor Freight Tools</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,497 +1361,497 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a333269a7a1a658e</t>
+          <t>https://www.indeed.com/viewjob?jk=65c6bb88e77fa7e3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI &amp; Automation Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Stored Energy Systems</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Git, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14fb94404a5ee275</t>
+          <t>https://www.indeed.com/viewjob?jk=0426526011ecf8ab</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Scientist Geospatial Analytics</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bunge</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chesterfield, MO, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, BigQuery, BigQuery, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0df42bfc02a5f701</t>
+          <t>https://www.indeed.com/viewjob?jk=e2f4ae59bb2e76db</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NewYork-Presbyterian Hospital</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a889968da2ddc13e</t>
+          <t>https://www.indeed.com/viewjob?jk=fc596e52195e0933</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Associate</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Git, Kafka, Cassandra, NoSQL, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaad1b10fdb8d092</t>
+          <t>https://www.indeed.com/viewjob?jk=44f8b5180e01e140</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DevOps and Site Reliability Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58a6a360953a1f79</t>
+          <t>https://www.indeed.com/viewjob?jk=af0b8f364ebc3247</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer - Automation, Early Career</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e05d0af611ab8d76</t>
+          <t>https://www.indeed.com/viewjob?jk=ef9c01896959f630</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Yield Solutions Group LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Centennial, CO, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, CI/CD, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68121ab049612e6f</t>
+          <t>https://www.indeed.com/viewjob?jk=271061dada6a961f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Full Stack Python Developer Active Secret Clearance Requ Herndon VA</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Innovative Tech Solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, Databricks, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6dc3bdf5d64e1ba</t>
+          <t>https://www.indeed.com/viewjob?jk=1faf6e04fa2bbdcf</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI (.Net)</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce369a125b1def8c</t>
+          <t>https://www.indeed.com/viewjob?jk=f9794568eb039870</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI (.Net)</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=146470e0e0fd5922</t>
+          <t>https://www.indeed.com/viewjob?jk=1560887d7cb316fd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Quality Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Momentive Software</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Gemini, Pinecone, Prompt Engineering, CI/CD, Git, Python, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81175184ac69abaa</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd4ac5f09111b4e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Keras, spaCy, MLflow, FastAPI, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3b161f030038d4e</t>
+          <t>https://www.indeed.com/viewjob?jk=dee274917e4b9029</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr Scientist, Tech</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PySpark, Hadoop, Tableau, Matplotlib, Python, SQL, R, Scala, Optimization, A/B Testing</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d43651fd738ad37a</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1f0804f082a435</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Asylon</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norristown, PA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6713335c51820324</t>
+          <t>https://www.indeed.com/viewjob?jk=2bcfef10dd24abe4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Frontend Engineer/UX Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Asylon</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norristown, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RAG, Git, MongoDB, NoSQL, Python, SQL, R, Java, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e01952c4a3f71b76</t>
+          <t>https://www.indeed.com/viewjob?jk=71d3b83605c8a2df</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Gemini, Kubernetes, Git, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,287 +1931,812 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc29356aa7c08c47</t>
+          <t>https://www.indeed.com/viewjob?jk=940dcb7683294d7b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Application Software Engineer - Testing</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0af81836b7e21cc9</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb60bebb7779e64</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Development Engineer II – Geoprocessing and Map Viewer Analysis</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=712ad52a7ca693ad</t>
+          <t>https://www.indeed.com/viewjob?jk=c37d2114cee6dba4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Enterprise AI Enablement Engineer</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Zywave, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, CI/CD, Git, Snowflake, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd93b504042602c1</t>
+          <t>https://www.indeed.com/viewjob?jk=c39c8b726cdb22aa</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer III -Python Fullstack - AI/ML</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024da5907788aedb</t>
+          <t>https://www.indeed.com/viewjob?jk=bd9a756aa23e011c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (Onsite Hybrid)</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, GitHub Actions, Git, Databricks, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5812a02c32719af</t>
+          <t>https://www.indeed.com/viewjob?jk=22d070dab1e1cb93</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Mgr. Software Engineering</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>UKG</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d930713a7cd6b8b</t>
+          <t>https://www.indeed.com/viewjob?jk=4045cf1c680be7b6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Assistant Research Scientist PREP0004601</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Johns Hopkins University</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Git, PostgreSQL, MongoDB, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bfda1b82787c0e2</t>
+          <t>https://www.indeed.com/viewjob?jk=d5f4daad7fda9ff7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Long Island City, New York</t>
+          <t>Software Engineer - Search and Personalization</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Bloomingdale's</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0671107537ae859</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Software Engineer - Search and Personalization</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ME, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a057a8d1dc27a54f</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Software Engineer - Search and Personalization</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>UT, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ec8eebe082d41ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Software Engineer - Search and Personalization</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3912346602551520</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Software Engineer - Search and Personalization</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AL, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c6b2ae9b514e3c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Software Engineer - Search and Personalization</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>CO, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cdeb6923f62c2160</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Software Engineer - Search and Personalization</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>RI, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e8bc2ea076a0ded7</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Software Engineer - Search and Personalization</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>MT, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee0fd3306ac2ce34</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Software Engineer - Automation, Early Career</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Viasat</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Carlsbad, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f83d10cc8f109e2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Payment Accuracy</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, BigQuery, Git, BigQuery, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5abf0b6e427573c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Full-Stack AI Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf95a91debbec1ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Full Stack AI Engineer</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Ryan, LLC</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
         <v>10</v>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eac7651c61492267</t>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, FastAPI, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1444566d7ca27d31</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Full-Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CLERA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ded108879d5d23e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>AI Developer (Austin)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>State of Texas</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd74d70bec55fb9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Machine Learning Scientist II - Pricing &amp; Profitability Algorithms</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Wayfair</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>RAG, XGBoost, MLflow, Docker, Kubernetes, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d6886e1633410ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Evergreen: Senior AI Platform &amp; Data Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Ad Hoc</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Kubernetes, Git, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b7db6b3e9c56edf</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-26.xlsx
+++ b/daily_matches/job_matches_2026-06-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,47 +468,47 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Associate - AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Keras, spaCy</t>
+          <t>LangChain, RAG, S3, Docker, Kubernetes, Apache Airflow, Git, Snowflake, Databricks, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c986febe6201a3ba</t>
+          <t>https://www.indeed.com/viewjob?jk=0309d0101fc2195f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>U.S. Financial Technology</t>
+          <t>Netwrix</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,81 +517,81 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>AI Engineer, RAG, Gemini, Azure ML, Kubernetes, CI/CD, Terraform, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a593e5a13bf91848</t>
+          <t>https://www.indeed.com/viewjob?jk=304684b8a3782958</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>ThoughtSpot</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Manayunk, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, AWS SageMaker, AKS, Snowflake</t>
+          <t>RAG, Redshift, BigQuery, Synapse, Snowflake, BigQuery, Redshift, Tableau, MicroStrategy, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74ecbc2e66a148f</t>
+          <t>https://www.indeed.com/viewjob?jk=76055147a11b9ecd</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Robotics Data Engineer/Data Scientist</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, CI/CD, Kafka, Hadoop, PostgreSQL, Cassandra, Python, SQL</t>
+          <t>RAG, Terraform, Git, Kafka, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,1887 +601,1887 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7d4e995adafbb96</t>
+          <t>https://www.indeed.com/viewjob?jk=136ad2f86b0dfd63</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AI-Augmented Backend</t>
+          <t>Sr. Software Engineer, Enterprise Software</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, SQL, R, Java</t>
+          <t>Copilot, Docker, Kubernetes, Git, MySQL, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73c154bd36b952fa</t>
+          <t>https://www.indeed.com/viewjob?jk=424a613517dace69</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Support Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Asylon</t>
+          <t>Symbotic</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norristown, PA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S3, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c73c430d87b81058</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1cd7a110446150</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Machine Learning Engineer I</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>Gen Digital Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S3, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Machine Learning Engineer, RAG, BigQuery, Git, BigQuery, Python, SQL, R, A/B Testing</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25cb408b4789fdc2</t>
+          <t>https://www.indeed.com/viewjob?jk=081b170085ad111e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9a38e235659081</t>
+          <t>https://www.indeed.com/viewjob?jk=c28dc72a80284ec6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd0775a42f899524</t>
+          <t>https://www.indeed.com/viewjob?jk=6302bf10905cdd4c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b33138f7850dfefc</t>
+          <t>https://www.indeed.com/viewjob?jk=789653ee2652eca1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a342726a84e27f8e</t>
+          <t>https://www.indeed.com/viewjob?jk=68bdbe7bd3f53a4a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c186d8b7ac65fdf8</t>
+          <t>https://www.indeed.com/viewjob?jk=2262f078bf643e84</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95cc142f3e2617a6</t>
+          <t>https://www.indeed.com/viewjob?jk=80ee2318419c5935</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db16f20add9ea986</t>
+          <t>https://www.indeed.com/viewjob?jk=588188c7c62082b9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1382d06b80fb6867</t>
+          <t>https://www.indeed.com/viewjob?jk=570d0c750962292e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcad5c4e643319ff</t>
+          <t>https://www.indeed.com/viewjob?jk=b39203fd4dea3bad</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Fayetteville, AR, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40e64526422d931b</t>
+          <t>https://www.indeed.com/viewjob?jk=92dd90ece7181e3a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4d627fd3422104c</t>
+          <t>https://www.indeed.com/viewjob?jk=ee5ad01a76851f6e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fab8211cf6bde1e0</t>
+          <t>https://www.indeed.com/viewjob?jk=f2b8fe1dc10e7cbc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05bab721c73d545f</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fa2859d1a24f3d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85a706af297ba804</t>
+          <t>https://www.indeed.com/viewjob?jk=f7db4bdc1cdd0062</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13401bc8d0f3279e</t>
+          <t>https://www.indeed.com/viewjob?jk=3d398bfc6ed48ddd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31032458d140d1ae</t>
+          <t>https://www.indeed.com/viewjob?jk=903e93d194c097e0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115cfe00112809d8</t>
+          <t>https://www.indeed.com/viewjob?jk=c906f117555da2f0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=031a5b8865d1f458</t>
+          <t>https://www.indeed.com/viewjob?jk=3be0a13ec205ad9b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65c6bb88e77fa7e3</t>
+          <t>https://www.indeed.com/viewjob?jk=1e700f2272e843c6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0426526011ecf8ab</t>
+          <t>https://www.indeed.com/viewjob?jk=d465b16f7cd79411</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2f4ae59bb2e76db</t>
+          <t>https://www.indeed.com/viewjob?jk=8cab55fb5c5584c4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>Silicon Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc596e52195e0933</t>
+          <t>https://www.indeed.com/viewjob?jk=44eceb1a9a6747a6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44f8b5180e01e140</t>
+          <t>https://www.indeed.com/viewjob?jk=efb2e285ea3dbbb8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af0b8f364ebc3247</t>
+          <t>https://www.indeed.com/viewjob?jk=bce8bbd5a45f50ee</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9c01896959f630</t>
+          <t>https://www.indeed.com/viewjob?jk=3f7683b5c3dc845d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271061dada6a961f</t>
+          <t>https://www.indeed.com/viewjob?jk=9975405d63a357cc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1faf6e04fa2bbdcf</t>
+          <t>https://www.indeed.com/viewjob?jk=5559ccfcf5f0f4a5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9794568eb039870</t>
+          <t>https://www.indeed.com/viewjob?jk=64c642e8339e236b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1560887d7cb316fd</t>
+          <t>https://www.indeed.com/viewjob?jk=539c5f895e8d47f0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd4ac5f09111b4e</t>
+          <t>https://www.indeed.com/viewjob?jk=a3f08fdd6baa563a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>Florham Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dee274917e4b9029</t>
+          <t>https://www.indeed.com/viewjob?jk=5e1f149adb2318c0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Melville, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1f0804f082a435</t>
+          <t>https://www.indeed.com/viewjob?jk=1896e21e114a1ff6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bcfef10dd24abe4</t>
+          <t>https://www.indeed.com/viewjob?jk=623a5a95e99348de</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Toledo, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d3b83605c8a2df</t>
+          <t>https://www.indeed.com/viewjob?jk=26750155edbd0cc9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=940dcb7683294d7b</t>
+          <t>https://www.indeed.com/viewjob?jk=65b6f09863590243</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb60bebb7779e64</t>
+          <t>https://www.indeed.com/viewjob?jk=b92cb8a009e3d876</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c37d2114cee6dba4</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c9a21ce151f033</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39c8b726cdb22aa</t>
+          <t>https://www.indeed.com/viewjob?jk=7511006babcfcd1c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd9a756aa23e011c</t>
+          <t>https://www.indeed.com/viewjob?jk=b4b8eff90f3c759d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22d070dab1e1cb93</t>
+          <t>https://www.indeed.com/viewjob?jk=1e6c91da56bc7bc8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4045cf1c680be7b6</t>
+          <t>https://www.indeed.com/viewjob?jk=b72ff65f89c6e867</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5f4daad7fda9ff7</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c78c5a8cd7b5ae</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0671107537ae859</t>
+          <t>https://www.indeed.com/viewjob?jk=9bbf77faa0245095</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a057a8d1dc27a54f</t>
+          <t>https://www.indeed.com/viewjob?jk=666a9564404ef4fc</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec8eebe082d41ed</t>
+          <t>https://www.indeed.com/viewjob?jk=d4c019aff6b88326</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3912346602551520</t>
+          <t>https://www.indeed.com/viewjob?jk=3d808a20402d92a9</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>Spartanburg, SC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c6b2ae9b514e3c3</t>
+          <t>https://www.indeed.com/viewjob?jk=1c36e556343e5d0b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdeb6923f62c2160</t>
+          <t>https://www.indeed.com/viewjob?jk=5df15e5c718ddb7d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8bc2ea076a0ded7</t>
+          <t>https://www.indeed.com/viewjob?jk=018953dcf3a26239</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer - Search and Personalization</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee0fd3306ac2ce34</t>
+          <t>https://www.indeed.com/viewjob?jk=29605573efbff072</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer - Automation, Early Career</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Viasat</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,94 +2491,94 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f83d10cc8f109e2b</t>
+          <t>https://www.indeed.com/viewjob?jk=1888f74301553484</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Payment Accuracy</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, BigQuery, Git, BigQuery, Python, SQL, R, Optimization</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5abf0b6e427573c0</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8ed8a9f835cdf8</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Full-Stack AI Engineer</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf95a91debbec1ca</t>
+          <t>https://www.indeed.com/viewjob?jk=25e9015d543ccd60</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full Stack AI Engineer</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ryan, LLC</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, FastAPI, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1444566d7ca27d31</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7883fdf3310f4a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded108879d5d23e5</t>
+          <t>https://www.indeed.com/viewjob?jk=ee8d9d4aa0cf2f56</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI Developer (Austin)</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>State of Texas</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, R, Java</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd74d70bec55fb9b</t>
+          <t>https://www.indeed.com/viewjob?jk=5cba02608200fc49</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Machine Learning Scientist II - Pricing &amp; Profitability Algorithms</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RAG, XGBoost, MLflow, Docker, Kubernetes, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d6886e1633410ef</t>
+          <t>https://www.indeed.com/viewjob?jk=e35c79732017d0c7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Evergreen: Senior AI Platform &amp; Data Engineer</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ad Hoc</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Kubernetes, Git, Databricks, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,322 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b7db6b3e9c56edf</t>
+          <t>https://www.indeed.com/viewjob?jk=00198432b4ea9904</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>US Tech - AI Engineering Senior Associate</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d62f21354c19ea71</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>US Tech - AI Engineering Senior Associate</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6de07d5d476e1a45</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>US Tech - AI Engineering Senior Associate</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=980ca63aa9f4cfba</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>US Tech - AI Engineering Senior Associate</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41d42d2398b8128a</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>US Tech - AI Engineering Senior Associate</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d36597846821f0f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>US Tech - AI Engineering Senior Associate</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3853690ac0837331</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>US Tech - AI Engineering Senior Associate</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76aa2dee85963073</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>US Tech - AI Engineering Senior Associate</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Columbia, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b645272372062ea2</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Software Support Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Symbotic</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Wilmington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, SQL, R</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef82234784cd4b19</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-26.xlsx
+++ b/daily_matches/job_matches_2026-06-26.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer - AI Agents</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Particle41</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.3</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, FAISS, Pinecone, TensorFlow, PyTorch, MLflow, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, Mistral, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6a7fc3bedd441c</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf847758389f80f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Software Engineer - AI Agents</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LogicMonitor</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Hugging Face, Prompt Engineering, Docker, Kubernetes, Git, Python, R</t>
+          <t>Data Scientist, Generative AI, LangChain, Mistral, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a9297029092a743</t>
+          <t>https://www.indeed.com/viewjob?jk=75a7d6d34e706b93</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HHAeXchange</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, PostgreSQL, NoSQL, Python, SQL</t>
+          <t>RAG, Data Lake, CI/CD, Jenkins, Terraform, Git, Snowflake, Databricks, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127acd5f3f140637</t>
+          <t>https://www.indeed.com/viewjob?jk=0631739ce734e7c7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Innovation Engineer</t>
+          <t>Software Engineer, Data Engineering</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>University of Wisconsin–Madison</t>
+          <t>Fubo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
+          <t>RAG, Redshift, BigQuery, Docker, Kubernetes, Snowflake, BigQuery, Redshift, Kafka, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd7d0b11ec243596</t>
+          <t>https://www.indeed.com/viewjob?jk=0e24be3cd83341f1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management - Software Engineering - Associate - Richardson</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>WISE EQUATION SOLUTION INC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Git, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Glue, Redshift, Git, Snowflake, Databricks, Redshift, PySpark, Tableau</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fadc871eddfaef1</t>
+          <t>https://www.indeed.com/viewjob?jk=9e83fcc84b022f15</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I</t>
+          <t>Senior Software Engineer | Middleware</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EnergyHub</t>
+          <t>ExtraHop Networks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CI/CD, GitHub Actions, Git, PostgreSQL, MongoDB, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, S3, EC2, FastAPI, Docker, Kubernetes, Terraform, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1dc6d335fb8d74d</t>
+          <t>https://www.indeed.com/viewjob?jk=111ecbafdd773723</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Consumer Subscriptions</t>
+          <t>Senior Engineer, Invest Tech</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Xai</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization, A/B Testing</t>
+          <t>Copilot, S3, CI/CD, Git, Snowflake, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=735be9277b931974</t>
+          <t>https://www.indeed.com/viewjob?jk=418fe6804d9bbee5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Consumer Subscriptions</t>
+          <t>Senior Engineer, Invest Tech</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Xai</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization, A/B Testing</t>
+          <t>Copilot, S3, CI/CD, Git, Snowflake, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=542a2b47f04a99a0</t>
+          <t>https://www.indeed.com/viewjob?jk=455cbc0d06bec7dd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Digital Support Intelligent Automation Solutions Engineer</t>
+          <t>Senior Associate Solutions Designer, AI Engineering</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Autodesk</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Git, Snowflake, Power BI, Python, R, Java</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Docker, Kubernetes, Jenkins, Git, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,112 +776,707 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58d7403aed43089c</t>
+          <t>https://www.indeed.com/viewjob?jk=344eb1b1e9721411</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Gemini, Kubernetes, Git, Python, R, Scala</t>
+          <t>RAG, S3, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34c0b3742a8333ca</t>
+          <t>https://www.indeed.com/viewjob?jk=b49f50dbf2988c82</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MassMutual</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Springfield, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Python, SQL, R, Optimization, Bayesian</t>
+          <t>RAG, S3, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af055e66a992a58a</t>
+          <t>https://www.indeed.com/viewjob?jk=d75b791cf50c1184</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Expert Associate Partner - Advanced Industries</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, Python, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=776060619ca92d8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Portsmouth, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, Python, R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2362abd894783c27</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, Python, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=992a2c5f94075440</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Data Scientist – Machine Learning</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Quest Global</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Winston-Salem, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, MLflow, Docker, Kubernetes, CI/CD, Git, Snowflake, Python, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3eef04c90a5e4d47</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Veho Tech, Inc</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Redshift, Snowflake, Databricks, Redshift, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e445ae0164b57049</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f7ed0e7abe75bd65</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DevOps Engineer III, AI &amp; Business Automation</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TrueNAS</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Campbell, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Prompt Engineering, Docker, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27864e9a8aba3802</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>.Net FSD</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Copilot, Prompt Engineering, FastAPI, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24dca549c9d5fb03</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer – Oracle DB</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Eli Lilly</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=caa3611b23da5c7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Software Engineer III- Quality Tooling</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>UKG</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Sunrise, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, GitHub Actions, Git, PostgreSQL, MongoDB, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c51c26d00c0a20b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Audiohook</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Eden, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=860468a620ab70f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ThoughtFocus</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>10</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=541ca1d5abd2452e</t>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI Engineer, Redshift, CI/CD, Terraform, Snowflake, Redshift, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=003a00af01087866</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Kafka, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07f6458c16dd4a81</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Chandler, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b519fe2e14cbf11a</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9666c46cb8d97c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Software Engineer ll, Data Platform</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cohere Health</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>S3, Athena, CI/CD, Git, Kafka, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80e694b601457a09</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AI Quality Assurance Analyst Associate(Fellowship Program)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Teacher Retirement System of Texas</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, Copilot, Prompt Engineering, CI/CD, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e32d4104524e8a5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>US Tech - AI Engineering Senior Associate</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ebb68cbd3b93d4a</t>
         </is>
       </c>
     </row>
